--- a/backtest_runs/20260410_193731/by_symbol/PIL/PIL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PIL/PIL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-4884.33000000001</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>105141.4</v>
@@ -679,7 +679,7 @@
         <v>-514.1400000000004</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>104627.26</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>109511.59</v>
@@ -817,7 +817,7 @@
         <v>-12339.36</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>97172.23000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-771.2099999999949</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>103598.98</v>
@@ -1277,7 +1277,7 @@
         <v>-10025.73</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>96658.09000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-4627.260000000004</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>98457.58</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>98714.65000000001</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>98714.65000000001</v>
